--- a/Versão5/ABNT/Ontologia_15965_0P.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_0P.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5762B82C-AAD9-43CC-8EBA-8C07D5FDB7F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BC2424-DC15-4594-800C-5776D3BF38B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22103" uniqueCount="2358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22103" uniqueCount="2361">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -7168,13 +7168,22 @@
   </si>
   <si>
     <t>Código.ABNT</t>
+  </si>
+  <si>
+    <t>0P.10.10.00</t>
+  </si>
+  <si>
+    <t>0P.10.40.00</t>
+  </si>
+  <si>
+    <t>0P.40.20.10.00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <color theme="1"/>
@@ -7253,6 +7262,12 @@
       <b/>
       <sz val="5"/>
       <color rgb="FF000000"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial Nova Cond Light"/>
       <family val="2"/>
     </font>
@@ -7467,7 +7482,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7626,12 +7641,15 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{C72A53DB-08DB-43C0-BB1A-395247558D94}"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
     <dxf>
       <font>
         <b val="0"/>
@@ -7639,6 +7657,16 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -8212,7 +8240,7 @@
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46139.326550925929</v>
+        <v>46146.29439988426</v>
       </c>
       <c r="C18" s="51" t="s">
         <v>2341</v>
@@ -8510,12 +8538,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:K2">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1:AA2">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8668,7 +8696,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8713,7 +8741,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9077,7 +9105,7 @@
       <c r="A6" s="5">
         <v>6</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="54" t="s">
         <v>1134</v>
       </c>
       <c r="C6" s="10" t="s">
@@ -9142,8 +9170,8 @@
       <c r="A7" s="5">
         <v>7</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>1134</v>
+      <c r="B7" s="54" t="s">
+        <v>2358</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>2357</v>
@@ -10702,8 +10730,8 @@
       <c r="A31" s="5">
         <v>31</v>
       </c>
-      <c r="B31" s="11" t="s">
-        <v>1158</v>
+      <c r="B31" s="54" t="s">
+        <v>2359</v>
       </c>
       <c r="C31" s="10" t="s">
         <v>2357</v>
@@ -10767,7 +10795,7 @@
       <c r="A32" s="5">
         <v>32</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="54" t="s">
         <v>1158</v>
       </c>
       <c r="C32" s="10" t="s">
@@ -20517,7 +20545,7 @@
       <c r="A182" s="5">
         <v>182</v>
       </c>
-      <c r="B182" s="11" t="s">
+      <c r="B182" s="54" t="s">
         <v>1308</v>
       </c>
       <c r="C182" s="10" t="s">
@@ -20582,8 +20610,8 @@
       <c r="A183" s="5">
         <v>183</v>
       </c>
-      <c r="B183" s="11" t="s">
-        <v>1308</v>
+      <c r="B183" s="54" t="s">
+        <v>2360</v>
       </c>
       <c r="C183" s="10" t="s">
         <v>2357</v>
@@ -80055,8 +80083,11 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="R1:U1048576">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_0P.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_0P.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD30223-F434-457D-AB57-751F2F339DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE2E0532-42FE-400E-80A5-FA12D69D4ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -8498,7 +8498,7 @@
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46157.684383912034</v>
+        <v>46158.489587962962</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>2297</v>

--- a/Versão5/ABNT/Ontologia_15965_0P.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_0P.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{858D112A-5258-48FD-8D59-072B3347102C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8AC64E9-EB35-442C-9860-1C6F025963E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25463" uniqueCount="2676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25463" uniqueCount="2675">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -8101,9 +8101,6 @@
   </si>
   <si>
     <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
-  </si>
-  <si>
-    <t>Arquitetura</t>
   </si>
   <si>
     <t>[ 5I ]</t>
@@ -8590,63 +8587,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{C72A53DB-08DB-43C0-BB1A-395247558D94}"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <font>
         <b val="0"/>
@@ -9297,7 +9238,7 @@
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46216.267478935188</v>
+        <v>46219.567509259257</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>2290</v>
@@ -9402,31 +9343,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{170652AC-F0FE-468B-8FA8-41F8E2A0F99B}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA67"/>
-  <sheetFormatPr defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.1640625" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" customWidth="1"/>
-    <col min="6" max="6" width="19.83203125" customWidth="1"/>
-    <col min="7" max="11" width="8.5" customWidth="1"/>
-    <col min="12" max="12" width="10.33203125" customWidth="1"/>
-    <col min="13" max="13" width="7.5" customWidth="1"/>
-    <col min="14" max="14" width="9.1640625" customWidth="1"/>
-    <col min="15" max="15" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="57.6640625" customWidth="1"/>
-    <col min="17" max="17" width="45.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.83203125" style="54" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.1640625" style="54" customWidth="1"/>
-    <col min="24" max="24" width="8.33203125" customWidth="1"/>
-    <col min="25" max="25" width="8.1640625" customWidth="1"/>
-    <col min="26" max="26" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="64.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="75.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="56.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5" style="54" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.83203125" style="54" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="79.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="34.35" customHeight="1" x14ac:dyDescent="0.2">
@@ -9512,7 +9453,7 @@
         <v>2285</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="54" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" s="54" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="44">
         <v>2</v>
       </c>
@@ -9584,7 +9525,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V2" s="36" t="s">
-        <v>2670</v>
+        <v>2311</v>
       </c>
       <c r="W2" s="53" t="str">
         <f>CONCATENATE("Key-ABNT-",A2)</f>
@@ -9597,14 +9538,14 @@
         <v>2224</v>
       </c>
       <c r="Z2" s="36" t="s">
-        <v>2671</v>
+        <v>2670</v>
       </c>
       <c r="AA2" s="36" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="54" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" s="54" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="44">
         <v>3</v>
       </c>
@@ -9655,7 +9596,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="36" t="s">
-        <v>2672</v>
+        <v>2671</v>
       </c>
       <c r="Q3" s="36" t="s">
         <v>2669</v>
@@ -9676,7 +9617,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V3" s="36" t="s">
-        <v>2670</v>
+        <v>2311</v>
       </c>
       <c r="W3" s="53" t="str">
         <f t="shared" ref="W3:W66" si="4">CONCATENATE("Key-ABNT-",A3)</f>
@@ -9696,7 +9637,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="54" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" s="54" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="44">
         <v>4</v>
       </c>
@@ -9747,7 +9688,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="36" t="s">
-        <v>2673</v>
+        <v>2672</v>
       </c>
       <c r="Q4" s="36" t="s">
         <v>2669</v>
@@ -9768,7 +9709,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V4" s="36" t="s">
-        <v>2670</v>
+        <v>2311</v>
       </c>
       <c r="W4" s="53" t="str">
         <f t="shared" si="4"/>
@@ -9788,7 +9729,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="54" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" s="54" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="44">
         <v>5</v>
       </c>
@@ -9839,7 +9780,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="36" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="Q5" s="36" t="s">
         <v>2669</v>
@@ -9860,7 +9801,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V5" s="36" t="s">
-        <v>2670</v>
+        <v>2311</v>
       </c>
       <c r="W5" s="53" t="str">
         <f t="shared" si="4"/>
@@ -9880,7 +9821,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="54" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" s="54" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="44">
         <v>6</v>
       </c>
@@ -9931,7 +9872,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="36" t="s">
-        <v>2675</v>
+        <v>2674</v>
       </c>
       <c r="Q6" s="36" t="s">
         <v>2669</v>
@@ -9952,7 +9893,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V6" s="36" t="s">
-        <v>2670</v>
+        <v>2311</v>
       </c>
       <c r="W6" s="53" t="str">
         <f t="shared" si="4"/>
@@ -9972,7 +9913,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="44">
         <v>7</v>
       </c>
@@ -10063,7 +10004,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="44">
         <v>8</v>
       </c>
@@ -10154,7 +10095,7 @@
         <v>2319</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="44">
         <v>9</v>
       </c>
@@ -10245,7 +10186,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="44">
         <v>10</v>
       </c>
@@ -10336,7 +10277,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="44">
         <v>11</v>
       </c>
@@ -10427,7 +10368,7 @@
         <v>2330</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="44">
         <v>12</v>
       </c>
@@ -10518,7 +10459,7 @@
         <v>2334</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="44">
         <v>13</v>
       </c>
@@ -10609,7 +10550,7 @@
         <v>2334</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="44">
         <v>14</v>
       </c>
@@ -10700,7 +10641,7 @@
         <v>2334</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="44">
         <v>15</v>
       </c>
@@ -10791,7 +10732,7 @@
         <v>2340</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="44">
         <v>16</v>
       </c>
@@ -10882,7 +10823,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="44">
         <v>17</v>
       </c>
@@ -10973,7 +10914,7 @@
         <v>2348</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="44">
         <v>18</v>
       </c>
@@ -11064,7 +11005,7 @@
         <v>2352</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="44">
         <v>19</v>
       </c>
@@ -11155,7 +11096,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="44">
         <v>20</v>
       </c>
@@ -11246,7 +11187,7 @@
         <v>2478</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="44">
         <v>21</v>
       </c>
@@ -11337,7 +11278,7 @@
         <v>2479</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="44">
         <v>22</v>
       </c>
@@ -11428,7 +11369,7 @@
         <v>2480</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="44">
         <v>23</v>
       </c>
@@ -11519,7 +11460,7 @@
         <v>2481</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="44">
         <v>24</v>
       </c>
@@ -11610,7 +11551,7 @@
         <v>2482</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="44">
         <v>25</v>
       </c>
@@ -11701,7 +11642,7 @@
         <v>2488</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="44">
         <v>26</v>
       </c>
@@ -11792,7 +11733,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="44">
         <v>27</v>
       </c>
@@ -11883,7 +11824,7 @@
         <v>2483</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="44">
         <v>28</v>
       </c>
@@ -11974,7 +11915,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="44">
         <v>29</v>
       </c>
@@ -12065,7 +12006,7 @@
         <v>2485</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="44">
         <v>30</v>
       </c>
@@ -12156,7 +12097,7 @@
         <v>2486</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="44">
         <v>31</v>
       </c>
@@ -12247,7 +12188,7 @@
         <v>2487</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="44">
         <v>32</v>
       </c>
@@ -12338,7 +12279,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="44">
         <v>33</v>
       </c>
@@ -12429,7 +12370,7 @@
         <v>2490</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="44">
         <v>34</v>
       </c>
@@ -12520,7 +12461,7 @@
         <v>2492</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="44">
         <v>35</v>
       </c>
@@ -12611,7 +12552,7 @@
         <v>2569</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="44">
         <v>36</v>
       </c>
@@ -12702,7 +12643,7 @@
         <v>2493</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="44">
         <v>37</v>
       </c>
@@ -12793,7 +12734,7 @@
         <v>2595</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="44">
         <v>38</v>
       </c>
@@ -12884,7 +12825,7 @@
         <v>2494</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="44">
         <v>39</v>
       </c>
@@ -12975,7 +12916,7 @@
         <v>2495</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="44">
         <v>40</v>
       </c>
@@ -13066,7 +13007,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="44">
         <v>41</v>
       </c>
@@ -13157,7 +13098,7 @@
         <v>2497</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="44">
         <v>42</v>
       </c>
@@ -13248,7 +13189,7 @@
         <v>2491</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="44">
         <v>43</v>
       </c>
@@ -13339,7 +13280,7 @@
         <v>2498</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="44">
         <v>44</v>
       </c>
@@ -13430,7 +13371,7 @@
         <v>2571</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="44">
         <v>45</v>
       </c>
@@ -13521,7 +13462,7 @@
         <v>2547</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="44">
         <v>46</v>
       </c>
@@ -13612,7 +13553,7 @@
         <v>2546</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="44">
         <v>47</v>
       </c>
@@ -13703,7 +13644,7 @@
         <v>2545</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="44">
         <v>48</v>
       </c>
@@ -13794,7 +13735,7 @@
         <v>2499</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="44">
         <v>49</v>
       </c>
@@ -13885,7 +13826,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="44">
         <v>50</v>
       </c>
@@ -13976,7 +13917,7 @@
         <v>2501</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="44">
         <v>51</v>
       </c>
@@ -14067,7 +14008,7 @@
         <v>2502</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="44">
         <v>52</v>
       </c>
@@ -14158,7 +14099,7 @@
         <v>2507</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="44">
         <v>53</v>
       </c>
@@ -14249,7 +14190,7 @@
         <v>2596</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="44">
         <v>54</v>
       </c>
@@ -14340,7 +14281,7 @@
         <v>2508</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="44">
         <v>55</v>
       </c>
@@ -14431,7 +14372,7 @@
         <v>2509</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="44">
         <v>56</v>
       </c>
@@ -14522,7 +14463,7 @@
         <v>2510</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="44">
         <v>57</v>
       </c>
@@ -14613,7 +14554,7 @@
         <v>2597</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="44">
         <v>58</v>
       </c>
@@ -14704,7 +14645,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="44">
         <v>59</v>
       </c>
@@ -14795,7 +14736,7 @@
         <v>2598</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="44">
         <v>60</v>
       </c>
@@ -14886,7 +14827,7 @@
         <v>2599</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="44">
         <v>61</v>
       </c>
@@ -14977,7 +14918,7 @@
         <v>2601</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="44">
         <v>62</v>
       </c>
@@ -15068,7 +15009,7 @@
         <v>2503</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="44">
         <v>63</v>
       </c>
@@ -15159,7 +15100,7 @@
         <v>2504</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="44">
         <v>64</v>
       </c>
@@ -15250,7 +15191,7 @@
         <v>2585</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="44">
         <v>65</v>
       </c>
@@ -15341,7 +15282,7 @@
         <v>2586</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="44">
         <v>66</v>
       </c>
@@ -15432,7 +15373,7 @@
         <v>2505</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="44">
         <v>67</v>
       </c>
@@ -15524,35 +15465,25 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A7:A67">
-    <cfRule type="cellIs" dxfId="17" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20:F67">
-    <cfRule type="duplicateValues" dxfId="12" priority="51"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F68:F1048576 F1 F7:F19">
-    <cfRule type="duplicateValues" dxfId="11" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1 AA7:AA67">
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
+  <conditionalFormatting sqref="A2:B67">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B6 B7:B67">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+  <conditionalFormatting sqref="F20:F67">
+    <cfRule type="duplicateValues" dxfId="6" priority="51"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+  <conditionalFormatting sqref="F68:F1048576 F1 F7:F19">
+    <cfRule type="duplicateValues" dxfId="5" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA1:AA67">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15705,7 +15636,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15750,7 +15681,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -93679,10 +93610,10 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1097">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:W1097">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_0P.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_0P.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A1D20B-9E79-4A06-AAA1-C626F48175CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546134AA-0F28-4FDF-98D2-613C8489317C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="9" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25463" uniqueCount="2680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25502" uniqueCount="2706">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -8131,13 +8131,91 @@
   </si>
   <si>
     <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 5I. Códigos de información de edificación.</t>
+  </si>
+  <si>
+    <t>Fonte1</t>
+  </si>
+  <si>
+    <t>https://brasil.un.org/pt-br/sdgs</t>
+  </si>
+  <si>
+    <t>Fonte2</t>
+  </si>
+  <si>
+    <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
+  </si>
+  <si>
+    <t>Fonte3</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
+  </si>
+  <si>
+    <t>FonteVegetação1</t>
+  </si>
+  <si>
+    <t>https://museunacional.ufrj.br/hortobotanico</t>
+  </si>
+  <si>
+    <t>FonteVegetação2</t>
+  </si>
+  <si>
+    <t>https://www.embrapa.br/florestas/publicacoes</t>
+  </si>
+  <si>
+    <t>FonteVegetação3</t>
+  </si>
+  <si>
+    <t>https://www.arvoresgigantes.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação4</t>
+  </si>
+  <si>
+    <t>https://www.scielo.br/j/abb</t>
+  </si>
+  <si>
+    <t>FonteVegetação5</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
+  </si>
+  <si>
+    <t>FonteVegetação6</t>
+  </si>
+  <si>
+    <t>https://botanicasaopaulo.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação7</t>
+  </si>
+  <si>
+    <t>https://pesquisa.in.gov.br/imprensa</t>
+  </si>
+  <si>
+    <t>FonteVegetação8</t>
+  </si>
+  <si>
+    <t>https://mapas.florestal.gov.br</t>
+  </si>
+  <si>
+    <t>FonteTSB</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
+  </si>
+  <si>
+    <t>FonteSINAPI</t>
+  </si>
+  <si>
+    <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <color theme="1"/>
@@ -8219,8 +8297,34 @@
       <name val="Arial Nova Cond Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color theme="10"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial Nova Cond"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="6"/>
+      <color theme="10"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8377,6 +8481,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -8426,11 +8536,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8597,8 +8708,27 @@
     <xf numFmtId="0" fontId="7" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="16" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{C72A53DB-08DB-43C0-BB1A-395247558D94}"/>
   </cellStyles>
@@ -9049,7 +9179,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2322550-D78D-4FAF-A04E-A74F4D7FBCA9}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" style="41" bestFit="1" customWidth="1"/>
@@ -9253,7 +9383,7 @@
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46232.77952708333</v>
+        <v>46233.478127662034</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>2289</v>
@@ -9349,7 +9479,157 @@
         <v>2291</v>
       </c>
     </row>
+    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="37" t="s">
+        <v>2680</v>
+      </c>
+      <c r="B27" s="56" t="s">
+        <v>2681</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="37" t="s">
+        <v>2682</v>
+      </c>
+      <c r="B28" s="57" t="s">
+        <v>2683</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="37" t="s">
+        <v>2684</v>
+      </c>
+      <c r="B29" s="57" t="s">
+        <v>2685</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="37" t="s">
+        <v>2686</v>
+      </c>
+      <c r="B30" s="58" t="s">
+        <v>2687</v>
+      </c>
+      <c r="C30" s="40" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="37" t="s">
+        <v>2688</v>
+      </c>
+      <c r="B31" s="58" t="s">
+        <v>2689</v>
+      </c>
+      <c r="C31" s="40" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="37" t="s">
+        <v>2690</v>
+      </c>
+      <c r="B32" s="58" t="s">
+        <v>2691</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="37" t="s">
+        <v>2692</v>
+      </c>
+      <c r="B33" s="60" t="s">
+        <v>2693</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="37" t="s">
+        <v>2694</v>
+      </c>
+      <c r="B34" s="60" t="s">
+        <v>2695</v>
+      </c>
+      <c r="C34" s="40" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="37" t="s">
+        <v>2696</v>
+      </c>
+      <c r="B35" s="58" t="s">
+        <v>2697</v>
+      </c>
+      <c r="C35" s="40" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="37" t="s">
+        <v>2698</v>
+      </c>
+      <c r="B36" s="60" t="s">
+        <v>2699</v>
+      </c>
+      <c r="C36" s="40" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="37" t="s">
+        <v>2700</v>
+      </c>
+      <c r="B37" s="58" t="s">
+        <v>2701</v>
+      </c>
+      <c r="C37" s="40" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="14" t="s">
+        <v>2702</v>
+      </c>
+      <c r="B38" s="61" t="s">
+        <v>2703</v>
+      </c>
+      <c r="C38" s="40" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="63" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="37" t="s">
+        <v>2704</v>
+      </c>
+      <c r="B39" s="62" t="s">
+        <v>2705</v>
+      </c>
+      <c r="C39" s="40" t="s">
+        <v>2289</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{01675649-0B10-4D9B-B1B9-91CED283B6A4}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{268A91DE-9D9B-4B7F-AC89-6C53A37EE04B}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{42FFFE3C-FC94-4167-B25B-82CF5F9FD355}"/>
+    <hyperlink ref="B38" r:id="rId4" xr:uid="{9AEFB983-DFE9-4646-A3B0-F6BF7F816E51}"/>
+    <hyperlink ref="B39" r:id="rId5" location="categoria_888" xr:uid="{6C613C90-96D6-4905-92DA-13CE9DD900CA}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
